--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/IOWA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/IOWA_2018.xlsx
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C96">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C169">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C455">
@@ -13009,7 +13009,7 @@
         <v>28</v>
       </c>
       <c r="D703">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="704">
